--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -709,7 +709,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I3" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"встраиваемый в Армстронг")</f>
         <v>встраиваемый в Армстронг</v>
@@ -875,8 +878,8 @@
         <v>30</v>
       </c>
       <c r="BJ3" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2667.0)</f>
-        <v>2667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2854.0)</f>
+        <v>2854</v>
       </c>
       <c r="BK3" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -909,7 +912,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -1084,8 +1090,8 @@
         <v>10</v>
       </c>
       <c r="BJ4" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3624.0)</f>
-        <v>3624</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3878.0)</f>
+        <v>3878</v>
       </c>
       <c r="BK4" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1121,7 +1127,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I5" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"встраиваемый в Армстронг")</f>
         <v>встраиваемый в Армстронг</v>
@@ -1296,8 +1305,8 @@
         <v>2</v>
       </c>
       <c r="BJ5" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2420.0)</f>
-        <v>2420</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2589.0)</f>
+        <v>2589</v>
       </c>
       <c r="BK5" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1333,7 +1342,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I6" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"встраиваемый в Армстронг")</f>
         <v>встраиваемый в Армстронг</v>
@@ -1499,8 +1511,8 @@
         <v>15</v>
       </c>
       <c r="BJ6" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2087.0)</f>
-        <v>2087</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2233.0)</f>
+        <v>2233</v>
       </c>
       <c r="BK6" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1536,7 +1548,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I7" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"встраиваемый в Армстронг")</f>
         <v>встраиваемый в Армстронг</v>
@@ -1702,8 +1717,8 @@
         <v>30</v>
       </c>
       <c r="BJ7" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1334.0)</f>
-        <v>1334</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1427.0)</f>
+        <v>1427</v>
       </c>
       <c r="BK7" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1739,7 +1754,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I8" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"встраиваемый в грильято")</f>
         <v>встраиваемый в грильято</v>
@@ -1905,8 +1923,8 @@
         <v>30</v>
       </c>
       <c r="BJ8" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1381.0)</f>
-        <v>1381</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1478.0)</f>
+        <v>1478</v>
       </c>
       <c r="BK8" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1942,7 +1960,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I9" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"встраиваемый в Армстронг")</f>
         <v>встраиваемый в Армстронг</v>
@@ -2108,8 +2129,8 @@
         <v>15</v>
       </c>
       <c r="BJ9" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2087.0)</f>
-        <v>2087</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2233.0)</f>
+        <v>2233</v>
       </c>
       <c r="BK9" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2145,7 +2166,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I10" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"встраиваемый в грильято")</f>
         <v>встраиваемый в грильято</v>
@@ -2311,8 +2335,8 @@
         <v>15</v>
       </c>
       <c r="BJ10" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2142.0)</f>
-        <v>2142</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2292.0)</f>
+        <v>2292</v>
       </c>
       <c r="BK10" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2348,7 +2372,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I11" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -2523,8 +2550,8 @@
         <v>1</v>
       </c>
       <c r="BJ11" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1687.0)</f>
-        <v>1687</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1805.0)</f>
+        <v>1805</v>
       </c>
       <c r="BK11" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2560,7 +2587,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I12" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -2735,8 +2765,8 @@
         <v>2</v>
       </c>
       <c r="BJ12" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2707.0)</f>
-        <v>2707</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2896.0)</f>
+        <v>2896</v>
       </c>
       <c r="BK12" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2772,7 +2802,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I13" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -2947,8 +2980,8 @@
         <v>1</v>
       </c>
       <c r="BJ13" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2150.0)</f>
-        <v>2150</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2301.0)</f>
+        <v>2301</v>
       </c>
       <c r="BK13" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2984,7 +3017,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I14" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -3159,8 +3195,8 @@
         <v>18</v>
       </c>
       <c r="BJ14" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2385.0)</f>
-        <v>2385</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2552.0)</f>
+        <v>2552</v>
       </c>
       <c r="BK14" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -3196,7 +3232,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I15" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -3371,8 +3410,8 @@
         <v>2</v>
       </c>
       <c r="BJ15" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1687.0)</f>
-        <v>1687</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1805.0)</f>
+        <v>1805</v>
       </c>
       <c r="BK15" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -3408,7 +3447,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I16" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -3583,8 +3625,8 @@
         <v>1</v>
       </c>
       <c r="BJ16" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1687.0)</f>
-        <v>1687</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1805.0)</f>
+        <v>1805</v>
       </c>
       <c r="BK16" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -3620,7 +3662,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I17" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -3795,8 +3840,8 @@
         <v>4</v>
       </c>
       <c r="BJ17" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1687.0)</f>
-        <v>1687</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1805.0)</f>
+        <v>1805</v>
       </c>
       <c r="BK17" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -3832,7 +3877,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Российская Федерация")</f>
         <v>Российская Федерация</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Без бренда")</f>
+        <v>Без бренда</v>
+      </c>
       <c r="I18" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"накладной; подвесной")</f>
         <v>накладной; подвесной</v>
@@ -4007,8 +4055,8 @@
         <v>1</v>
       </c>
       <c r="BJ18" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2707.0)</f>
-        <v>2707</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2896.0)</f>
+        <v>2896</v>
       </c>
       <c r="BK18" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -8093,8 +8141,8 @@
         <v>354</v>
       </c>
       <c r="K39" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41.0)</f>
+        <v>41</v>
       </c>
       <c r="L39" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Wolta ЖКХ")</f>
@@ -12791,8 +12839,8 @@
         <v>879</v>
       </c>
       <c r="K126" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="L126" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"НБУ, НПБ под лампу")</f>
@@ -13601,8 +13649,8 @@
         <v>387</v>
       </c>
       <c r="K141" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="L141" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RSV-SPO Светильники Производство, упаковка (2 и 3 штуки)")</f>
@@ -16517,8 +16565,8 @@
         <v>3725</v>
       </c>
       <c r="K195" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),79.0)</f>
+        <v>79</v>
       </c>
       <c r="L195" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -16733,8 +16781,8 @@
         <v>213</v>
       </c>
       <c r="K199" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-12.0)</f>
-        <v>-12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-18.0)</f>
+        <v>-18</v>
       </c>
       <c r="L199" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Офисный светильник RSV-SPO-02, SPO-03 (Сталь)")</f>
@@ -21647,8 +21695,8 @@
         <v>5956</v>
       </c>
       <c r="K290" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.0)</f>
-        <v>43</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
+        <v>51</v>
       </c>
       <c r="L290" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -22943,8 +22991,8 @@
         <v>193</v>
       </c>
       <c r="K314" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
+        <v>29</v>
       </c>
       <c r="L314" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Лампы производство, упаковка")</f>
@@ -28883,8 +28931,8 @@
         <v>125</v>
       </c>
       <c r="K424" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="L424" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Wolta декоративные")</f>
@@ -32717,8 +32765,8 @@
         <v>1.5</v>
       </c>
       <c r="K495" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="L495" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Упаковка")</f>
@@ -33689,8 +33737,8 @@
         <v>1.5</v>
       </c>
       <c r="K513" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L513" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Упаковка")</f>
@@ -36119,8 +36167,8 @@
         <v>606</v>
       </c>
       <c r="K558" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="L558" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NEOX Светильники LED ДВО - Опал производство, упаковка")</f>
@@ -36281,8 +36329,8 @@
         <v>1629</v>
       </c>
       <c r="K561" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="L561" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Wolta прожекторы")</f>
@@ -38225,8 +38273,8 @@
         <v>1193</v>
       </c>
       <c r="K597" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-8.0)</f>
+        <v>-8</v>
       </c>
       <c r="L597" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Line Shell, Free (Retail) до 10.2025")</f>
@@ -41843,8 +41891,8 @@
         <v>2258</v>
       </c>
       <c r="K664" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="L664" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -43463,8 +43511,8 @@
         <v>6449</v>
       </c>
       <c r="K694" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.0)</f>
-        <v>31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="L694" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -47459,21 +47507,6 @@
       <c r="L775" s="2"/>
       <c r="M775" s="2"/>
     </row>
-    <row r="776">
-      <c r="A776" s="5"/>
-      <c r="B776" s="5"/>
-      <c r="C776" s="2"/>
-      <c r="D776" s="2"/>
-      <c r="E776" s="2"/>
-      <c r="F776" s="2"/>
-      <c r="G776" s="2"/>
-      <c r="H776" s="2"/>
-      <c r="I776" s="2"/>
-      <c r="J776" s="2"/>
-      <c r="K776" s="2"/>
-      <c r="L776" s="2"/>
-      <c r="M776" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -12677,8 +12677,8 @@
         <v>355</v>
       </c>
       <c r="K123" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="L123" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Светильник светодиодный серии DECO")</f>
@@ -12731,8 +12731,8 @@
         <v>879</v>
       </c>
       <c r="K124" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="L124" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"НБУ, НПБ под лампу")</f>
@@ -13595,8 +13595,8 @@
         <v>738</v>
       </c>
       <c r="K140" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L140" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Лампы производство, упаковка")</f>
@@ -16727,8 +16727,8 @@
         <v>450</v>
       </c>
       <c r="K198" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="L198" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Светильник светодиодный серии DECO")</f>
@@ -21263,8 +21263,8 @@
         <v>346</v>
       </c>
       <c r="K282" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),333.0)</f>
-        <v>333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.0)</f>
+        <v>332</v>
       </c>
       <c r="L282" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Приставные, настенные, регулируемые")</f>
@@ -21803,8 +21803,8 @@
         <v>2500</v>
       </c>
       <c r="K292" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="L292" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Practical+ Уличные GLERIO")</f>
@@ -22883,8 +22883,8 @@
         <v>193</v>
       </c>
       <c r="K312" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
-        <v>29</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="L312" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Лампы производство, упаковка")</f>
@@ -27365,8 +27365,8 @@
         <v>355</v>
       </c>
       <c r="K395" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="L395" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Светильник светодиодный серии DECO")</f>
@@ -29417,8 +29417,8 @@
         <v>1403</v>
       </c>
       <c r="K433" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="L433" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Wolta декоративные")</f>
@@ -32495,8 +32495,8 @@
         <v>218</v>
       </c>
       <c r="K490" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="L490" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ASD электромонтажные изделия")</f>
@@ -32657,8 +32657,8 @@
         <v>1.5</v>
       </c>
       <c r="K493" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.0)</f>
+        <v>97</v>
       </c>
       <c r="L493" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Упаковка")</f>
@@ -34547,8 +34547,8 @@
         <v>2873</v>
       </c>
       <c r="K528" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L528" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NEOX Светильники LED ДВО-PRO производство, упаковка")</f>
@@ -35897,8 +35897,8 @@
         <v>601</v>
       </c>
       <c r="K553" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L553" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -43349,8 +43349,8 @@
         <v>6449</v>
       </c>
       <c r="K691" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="L691" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -44645,8 +44645,8 @@
         <v>646</v>
       </c>
       <c r="K715" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L715" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NEOX Светильники LED ДВО - Опал производство, упаковка")</f>
@@ -46373,8 +46373,8 @@
         <v>1169</v>
       </c>
       <c r="K747" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="L747" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NEOX Светильники LED ДВО - Опал производство, упаковка")</f>
@@ -47345,66 +47345,6 @@
       <c r="L772" s="2"/>
       <c r="M772" s="2"/>
     </row>
-    <row r="773">
-      <c r="A773" s="5"/>
-      <c r="B773" s="5"/>
-      <c r="C773" s="2"/>
-      <c r="D773" s="2"/>
-      <c r="E773" s="2"/>
-      <c r="F773" s="2"/>
-      <c r="G773" s="2"/>
-      <c r="H773" s="2"/>
-      <c r="I773" s="2"/>
-      <c r="J773" s="2"/>
-      <c r="K773" s="2"/>
-      <c r="L773" s="2"/>
-      <c r="M773" s="2"/>
-    </row>
-    <row r="774">
-      <c r="A774" s="5"/>
-      <c r="B774" s="5"/>
-      <c r="C774" s="2"/>
-      <c r="D774" s="2"/>
-      <c r="E774" s="2"/>
-      <c r="F774" s="2"/>
-      <c r="G774" s="2"/>
-      <c r="H774" s="2"/>
-      <c r="I774" s="2"/>
-      <c r="J774" s="2"/>
-      <c r="K774" s="2"/>
-      <c r="L774" s="2"/>
-      <c r="M774" s="2"/>
-    </row>
-    <row r="775">
-      <c r="A775" s="5"/>
-      <c r="B775" s="5"/>
-      <c r="C775" s="2"/>
-      <c r="D775" s="2"/>
-      <c r="E775" s="2"/>
-      <c r="F775" s="2"/>
-      <c r="G775" s="2"/>
-      <c r="H775" s="2"/>
-      <c r="I775" s="2"/>
-      <c r="J775" s="2"/>
-      <c r="K775" s="2"/>
-      <c r="L775" s="2"/>
-      <c r="M775" s="2"/>
-    </row>
-    <row r="776">
-      <c r="A776" s="5"/>
-      <c r="B776" s="5"/>
-      <c r="C776" s="2"/>
-      <c r="D776" s="2"/>
-      <c r="E776" s="2"/>
-      <c r="F776" s="2"/>
-      <c r="G776" s="2"/>
-      <c r="H776" s="2"/>
-      <c r="I776" s="2"/>
-      <c r="J776" s="2"/>
-      <c r="K776" s="2"/>
-      <c r="L776" s="2"/>
-      <c r="M776" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -874,8 +874,8 @@
       <c r="BG3" s="2"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="BJ3" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2854.0)</f>
@@ -6085,8 +6085,8 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 20.10.2026 Stock")</f>
-        <v>Отчёт о товарах 20.10.2026 Stock</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 21.10.2026 Stock")</f>
+        <v>Отчёт о товарах 21.10.2026 Stock</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="2"/>
@@ -11111,8 +11111,8 @@
         <v>7105</v>
       </c>
       <c r="K94" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
-        <v>54</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
+        <v>48</v>
       </c>
       <c r="L94" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -16457,8 +16457,8 @@
         <v>3725</v>
       </c>
       <c r="K193" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
-        <v>167</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
+        <v>65</v>
       </c>
       <c r="L193" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -22721,8 +22721,8 @@
         <v>7186</v>
       </c>
       <c r="K309" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="L309" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -47345,21 +47345,6 @@
       <c r="L772" s="2"/>
       <c r="M772" s="2"/>
     </row>
-    <row r="773">
-      <c r="A773" s="5"/>
-      <c r="B773" s="5"/>
-      <c r="C773" s="2"/>
-      <c r="D773" s="2"/>
-      <c r="E773" s="2"/>
-      <c r="F773" s="2"/>
-      <c r="G773" s="2"/>
-      <c r="H773" s="2"/>
-      <c r="I773" s="2"/>
-      <c r="J773" s="2"/>
-      <c r="K773" s="2"/>
-      <c r="L773" s="2"/>
-      <c r="M773" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -6512,8 +6512,8 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 22.10.2026 Stock")</f>
-        <v>Отчёт о товарах 22.10.2026 Stock</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 23.10.2026 Stock")</f>
+        <v>Отчёт о товарах 23.10.2026 Stock</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="2"/>
@@ -10674,8 +10674,8 @@
         <v>636</v>
       </c>
       <c r="K78" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -13212,8 +13212,8 @@
         <v>879</v>
       </c>
       <c r="K125" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="L125" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"НБУ, НПБ под лампу")</f>
@@ -18180,8 +18180,8 @@
         <v>1110</v>
       </c>
       <c r="K217" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L217" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -21744,8 +21744,8 @@
         <v>346</v>
       </c>
       <c r="K283" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),319.0)</f>
-        <v>319</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),318.0)</f>
+        <v>318</v>
       </c>
       <c r="L283" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Приставные, настенные, регулируемые")</f>
@@ -41454,8 +41454,8 @@
         <v>2302</v>
       </c>
       <c r="K648" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="L648" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -42156,8 +42156,8 @@
         <v>2258</v>
       </c>
       <c r="K661" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="L661" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -47772,21 +47772,6 @@
       <c r="L772" s="2"/>
       <c r="M772" s="2"/>
     </row>
-    <row r="773">
-      <c r="A773" s="5"/>
-      <c r="B773" s="5"/>
-      <c r="C773" s="2"/>
-      <c r="D773" s="2"/>
-      <c r="E773" s="2"/>
-      <c r="F773" s="2"/>
-      <c r="G773" s="2"/>
-      <c r="H773" s="2"/>
-      <c r="I773" s="2"/>
-      <c r="J773" s="2"/>
-      <c r="K773" s="2"/>
-      <c r="L773" s="2"/>
-      <c r="M773" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -6512,8 +6512,8 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 23.10.2026 Stock")</f>
-        <v>Отчёт о товарах 23.10.2026 Stock</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 24.10.2026 Stock")</f>
+        <v>Отчёт о товарах 24.10.2026 Stock</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="2"/>
@@ -24390,8 +24390,8 @@
         <v>6095</v>
       </c>
       <c r="K332" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L332" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал")</f>
@@ -47124,8 +47124,8 @@
         <v>4140</v>
       </c>
       <c r="K753" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
-        <v>33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
       </c>
       <c r="L753" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал")</f>
@@ -47718,21 +47718,6 @@
       <c r="L771" s="2"/>
       <c r="M771" s="2"/>
     </row>
-    <row r="772">
-      <c r="A772" s="5"/>
-      <c r="B772" s="5"/>
-      <c r="C772" s="2"/>
-      <c r="D772" s="2"/>
-      <c r="E772" s="2"/>
-      <c r="F772" s="2"/>
-      <c r="G772" s="2"/>
-      <c r="H772" s="2"/>
-      <c r="I772" s="2"/>
-      <c r="J772" s="2"/>
-      <c r="K772" s="2"/>
-      <c r="L772" s="2"/>
-      <c r="M772" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -43884,8 +43884,8 @@
         <v>619</v>
       </c>
       <c r="K693" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L693" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Декоративные")</f>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -47610,36 +47610,6 @@
       <c r="L769" s="2"/>
       <c r="M769" s="2"/>
     </row>
-    <row r="770">
-      <c r="A770" s="5"/>
-      <c r="B770" s="5"/>
-      <c r="C770" s="2"/>
-      <c r="D770" s="2"/>
-      <c r="E770" s="2"/>
-      <c r="F770" s="2"/>
-      <c r="G770" s="2"/>
-      <c r="H770" s="2"/>
-      <c r="I770" s="2"/>
-      <c r="J770" s="2"/>
-      <c r="K770" s="2"/>
-      <c r="L770" s="2"/>
-      <c r="M770" s="2"/>
-    </row>
-    <row r="771">
-      <c r="A771" s="5"/>
-      <c r="B771" s="5"/>
-      <c r="C771" s="2"/>
-      <c r="D771" s="2"/>
-      <c r="E771" s="2"/>
-      <c r="F771" s="2"/>
-      <c r="G771" s="2"/>
-      <c r="H771" s="2"/>
-      <c r="I771" s="2"/>
-      <c r="J771" s="2"/>
-      <c r="K771" s="2"/>
-      <c r="L771" s="2"/>
-      <c r="M771" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -6512,8 +6512,8 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 25.10.2026 Stock")</f>
-        <v>Отчёт о товарах 25.10.2026 Stock</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 26.10.2026 Stock")</f>
+        <v>Отчёт о товарах 26.10.2026 Stock</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="2"/>
@@ -10620,8 +10620,8 @@
         <v>636</v>
       </c>
       <c r="K77" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -14184,8 +14184,8 @@
         <v>1044</v>
       </c>
       <c r="K143" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L143" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Прожекторы RSV-SFL-3")</f>
@@ -20016,8 +20016,8 @@
         <v>127</v>
       </c>
       <c r="K251" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="L251" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Smartbuy LED светильники")</f>
@@ -21690,8 +21690,8 @@
         <v>346</v>
       </c>
       <c r="K282" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),308.0)</f>
-        <v>308</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),307.0)</f>
+        <v>307</v>
       </c>
       <c r="L282" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Приставные, настенные, регулируемые")</f>
@@ -41076,8 +41076,8 @@
         <v>1640</v>
       </c>
       <c r="K641" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L641" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Уличное освещение RSV")</f>
@@ -41994,8 +41994,8 @@
         <v>2258</v>
       </c>
       <c r="K658" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="L658" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -6512,8 +6512,8 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 28.10.2026 Stock")</f>
-        <v>Отчёт о товарах 28.10.2026 Stock</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 29.10.2026 Stock")</f>
+        <v>Отчёт о товарах 29.10.2026 Stock</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="2"/>
@@ -18072,8 +18072,8 @@
         <v>1110</v>
       </c>
       <c r="K215" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L215" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -22198,8 +22198,8 @@
         <v>VRN-UNE-80-G40K67-U, 80Вт, Универсальный</v>
       </c>
       <c r="C292" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.148)</f>
-        <v>0.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.75)</f>
+        <v>1.75</v>
       </c>
       <c r="D292" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.00805)</f>
@@ -24278,8 +24278,8 @@
         <v>6385</v>
       </c>
       <c r="J330" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6095.0)</f>
-        <v>6095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6385.0)</f>
+        <v>6385</v>
       </c>
       <c r="K330" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
@@ -41724,8 +41724,8 @@
         <v>1334</v>
       </c>
       <c r="K653" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
+        <v>30</v>
       </c>
       <c r="L653" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Office Special+ GLERIO (Офис Премиум)")</f>
@@ -43668,8 +43668,8 @@
         <v>1032</v>
       </c>
       <c r="K689" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L689" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Декоративные")</f>
@@ -44600,110 +44600,110 @@
     </row>
     <row r="707">
       <c r="A707" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GL81211")</f>
+        <v>GL81211</v>
+      </c>
+      <c r="B707" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GLERIO Office Casual 30 Вт 4000K 81P-30D-4V-P")</f>
+        <v>GLERIO Office Casual 30 Вт 4000K 81P-30D-4V-P</v>
+      </c>
+      <c r="C707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.14)</f>
+        <v>1.14</v>
+      </c>
+      <c r="D707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.008190000000000001)</f>
+        <v>0.00819</v>
+      </c>
+      <c r="E707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2095.2)</f>
+        <v>2095.2</v>
+      </c>
+      <c r="F707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2420.0)</f>
+        <v>2420</v>
+      </c>
+      <c r="G707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3047.0)</f>
+        <v>3047</v>
+      </c>
+      <c r="H707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3422.0)</f>
+        <v>3422</v>
+      </c>
+      <c r="I707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3796.0)</f>
+        <v>3796</v>
+      </c>
+      <c r="J707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3047.0)</f>
+        <v>3047</v>
+      </c>
+      <c r="K707" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
+      </c>
+      <c r="L707" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Office Casual+ GLERIO (Офис)")</f>
+        <v>Office Casual+ GLERIO (Офис)</v>
+      </c>
+      <c r="M707" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"С равномерной засветкой, LED Светильники")</f>
+        <v>С равномерной засветкой, LED Светильники</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"4690612013497")</f>
         <v>4690612013497</v>
       </c>
-      <c r="B707" s="5" t="str">
+      <c r="B708" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ССО-03Б 9Вт сенсор-диммер ночник адаптер БЕЛЫЙ IN HOME")</f>
         <v>ССО-03Б 9Вт сенсор-диммер ночник адаптер БЕЛЫЙ IN HOME</v>
       </c>
-      <c r="C707" s="2">
+      <c r="C708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.62)</f>
         <v>0.62</v>
       </c>
-      <c r="D707" s="2">
+      <c r="D708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.004500000000000001)</f>
         <v>0.0045</v>
       </c>
-      <c r="E707" s="2">
+      <c r="E708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1090.33)</f>
         <v>1090.33</v>
       </c>
-      <c r="F707" s="2">
+      <c r="F708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),813.0)</f>
         <v>813</v>
       </c>
-      <c r="G707" s="2">
+      <c r="G708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),915.0)</f>
         <v>915</v>
       </c>
-      <c r="H707" s="2">
+      <c r="H708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1061.0)</f>
         <v>1061</v>
       </c>
-      <c r="I707" s="2">
+      <c r="I708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1220.0)</f>
         <v>1220</v>
       </c>
-      <c r="J707" s="2">
+      <c r="J708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),610.0)</f>
         <v>610</v>
       </c>
-      <c r="K707" s="2">
+      <c r="K708" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
         <v>6</v>
       </c>
-      <c r="L707" s="2" t="str">
+      <c r="L708" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Светильники настольные светодиодные")</f>
         <v>Светильники настольные светодиодные</v>
       </c>
-      <c r="M707" s="2" t="str">
+      <c r="M708" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Светильники общего назначения (LED), Декоративные, LED Светильники")</f>
         <v>Светильники общего назначения (LED), Декоративные, LED Светильники</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GL81211")</f>
-        <v>GL81211</v>
-      </c>
-      <c r="B708" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GLERIO Office Casual 30 Вт 4000K 81P-30D-4V-P")</f>
-        <v>GLERIO Office Casual 30 Вт 4000K 81P-30D-4V-P</v>
-      </c>
-      <c r="C708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.14)</f>
-        <v>1.14</v>
-      </c>
-      <c r="D708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.008190000000000001)</f>
-        <v>0.00819</v>
-      </c>
-      <c r="E708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2095.2)</f>
-        <v>2095.2</v>
-      </c>
-      <c r="F708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2420.0)</f>
-        <v>2420</v>
-      </c>
-      <c r="G708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3047.0)</f>
-        <v>3047</v>
-      </c>
-      <c r="H708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3422.0)</f>
-        <v>3422</v>
-      </c>
-      <c r="I708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3796.0)</f>
-        <v>3796</v>
-      </c>
-      <c r="J708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3047.0)</f>
-        <v>3047</v>
-      </c>
-      <c r="K708" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
-      </c>
-      <c r="L708" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Office Casual+ GLERIO (Офис)")</f>
-        <v>Office Casual+ GLERIO (Офис)</v>
-      </c>
-      <c r="M708" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"С равномерной засветкой, LED Светильники")</f>
-        <v>С равномерной засветкой, LED Светильники</v>
       </c>
     </row>
     <row r="709">
@@ -47448,36 +47448,6 @@
       <c r="L766" s="2"/>
       <c r="M766" s="2"/>
     </row>
-    <row r="767">
-      <c r="A767" s="5"/>
-      <c r="B767" s="5"/>
-      <c r="C767" s="2"/>
-      <c r="D767" s="2"/>
-      <c r="E767" s="2"/>
-      <c r="F767" s="2"/>
-      <c r="G767" s="2"/>
-      <c r="H767" s="2"/>
-      <c r="I767" s="2"/>
-      <c r="J767" s="2"/>
-      <c r="K767" s="2"/>
-      <c r="L767" s="2"/>
-      <c r="M767" s="2"/>
-    </row>
-    <row r="768">
-      <c r="A768" s="5"/>
-      <c r="B768" s="5"/>
-      <c r="C768" s="2"/>
-      <c r="D768" s="2"/>
-      <c r="E768" s="2"/>
-      <c r="F768" s="2"/>
-      <c r="G768" s="2"/>
-      <c r="H768" s="2"/>
-      <c r="I768" s="2"/>
-      <c r="J768" s="2"/>
-      <c r="K768" s="2"/>
-      <c r="L768" s="2"/>
-      <c r="M768" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -6094,8 +6094,8 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 29.10.2026 Stock")</f>
-        <v>Отчёт о товарах 29.10.2026 Stock</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE('Ссылки'!B2,""Лист1!A:M"")"),"Отчёт о товарах 30.10.2026 Stock")</f>
+        <v>Отчёт о товарах 30.10.2026 Stock</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="2"/>
@@ -7124,8 +7124,8 @@
         <v>625</v>
       </c>
       <c r="K20" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
       <c r="L20" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rexant")</f>
@@ -13442,8 +13442,8 @@
         <v>387</v>
       </c>
       <c r="K137" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="L137" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RSV-SPO Светильники Производство, упаковка (2 и 3 штуки)")</f>
@@ -15760,8 +15760,8 @@
         <v>695</v>
       </c>
       <c r="J180" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
-        <v>348</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),695.0)</f>
+        <v>695</v>
       </c>
       <c r="K180" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -16412,8 +16412,8 @@
         <v>3725</v>
       </c>
       <c r="K192" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
       </c>
       <c r="L192" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -20620,8 +20620,8 @@
         <v>36</v>
       </c>
       <c r="J270" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
       </c>
       <c r="K270" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21488,8 +21488,8 @@
         <v>5956</v>
       </c>
       <c r="K286" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
+        <v>47</v>
       </c>
       <c r="L286" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -22676,8 +22676,8 @@
         <v>7186</v>
       </c>
       <c r="K308" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="L308" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -23158,8 +23158,8 @@
         <v>2295</v>
       </c>
       <c r="J317" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1148.0)</f>
-        <v>1148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2295.0)</f>
+        <v>2295</v>
       </c>
       <c r="K317" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26938,8 +26938,8 @@
         <v>695</v>
       </c>
       <c r="J387" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.0)</f>
-        <v>348</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),695.0)</f>
+        <v>695</v>
       </c>
       <c r="K387" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -36716,8 +36716,8 @@
         <v>3225</v>
       </c>
       <c r="K568" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),213.0)</f>
-        <v>213</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),204.0)</f>
+        <v>204</v>
       </c>
       <c r="L568" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -42926,8 +42926,8 @@
         <v>6449</v>
       </c>
       <c r="K683" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41.0)</f>
-        <v>41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="L683" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Универсал Эконом")</f>
@@ -46544,8 +46544,8 @@
         <v>1048</v>
       </c>
       <c r="K750" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="L750" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Лампы производство, упаковка")</f>
@@ -46922,36 +46922,6 @@
       <c r="L764" s="2"/>
       <c r="M764" s="2"/>
     </row>
-    <row r="765">
-      <c r="A765" s="5"/>
-      <c r="B765" s="5"/>
-      <c r="C765" s="2"/>
-      <c r="D765" s="2"/>
-      <c r="E765" s="2"/>
-      <c r="F765" s="2"/>
-      <c r="G765" s="2"/>
-      <c r="H765" s="2"/>
-      <c r="I765" s="2"/>
-      <c r="J765" s="2"/>
-      <c r="K765" s="2"/>
-      <c r="L765" s="2"/>
-      <c r="M765" s="2"/>
-    </row>
-    <row r="766">
-      <c r="A766" s="5"/>
-      <c r="B766" s="5"/>
-      <c r="C766" s="2"/>
-      <c r="D766" s="2"/>
-      <c r="E766" s="2"/>
-      <c r="F766" s="2"/>
-      <c r="G766" s="2"/>
-      <c r="H766" s="2"/>
-      <c r="I766" s="2"/>
-      <c r="J766" s="2"/>
-      <c r="K766" s="2"/>
-      <c r="L766" s="2"/>
-      <c r="M766" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/latest_stock.xlsx
+++ b/data/latest_stock.xlsx
@@ -46544,36 +46544,6 @@
       <c r="L757" s="2"/>
       <c r="M757" s="2"/>
     </row>
-    <row r="758">
-      <c r="A758" s="5"/>
-      <c r="B758" s="5"/>
-      <c r="C758" s="2"/>
-      <c r="D758" s="2"/>
-      <c r="E758" s="2"/>
-      <c r="F758" s="2"/>
-      <c r="G758" s="2"/>
-      <c r="H758" s="2"/>
-      <c r="I758" s="2"/>
-      <c r="J758" s="2"/>
-      <c r="K758" s="2"/>
-      <c r="L758" s="2"/>
-      <c r="M758" s="2"/>
-    </row>
-    <row r="759">
-      <c r="A759" s="5"/>
-      <c r="B759" s="5"/>
-      <c r="C759" s="2"/>
-      <c r="D759" s="2"/>
-      <c r="E759" s="2"/>
-      <c r="F759" s="2"/>
-      <c r="G759" s="2"/>
-      <c r="H759" s="2"/>
-      <c r="I759" s="2"/>
-      <c r="J759" s="2"/>
-      <c r="K759" s="2"/>
-      <c r="L759" s="2"/>
-      <c r="M759" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
